--- a/data/trans_dic/P79$impuestos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79$impuestos_2023-Provincia-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,81</t>
+          <t>0,55; 3,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,95</t>
+          <t>1,67; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,95</t>
+          <t>1,33; 2,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,32</t>
+          <t>0,28; 2,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,81</t>
+          <t>0,37; 2,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,21</t>
+          <t>0,48; 2,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,38</t>
+          <t>0,41; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,05</t>
+          <t>0,23; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,65</t>
+          <t>0,46; 2,47</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,94</t>
+          <t>0,09; 0,95</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,1</t>
+          <t>0,13; 1,28</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,27</t>
+          <t>0,33; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,07</t>
+          <t>0,28; 1,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,28</t>
+          <t>0,42; 1,3</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,39</t>
+          <t>1,76; 4,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,47</t>
+          <t>1,44; 3,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,98</t>
+          <t>1,75; 3,37</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,76</t>
+          <t>1,0; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,53</t>
+          <t>0,93; 1,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,47</t>
+          <t>1,07; 1,63</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 4501</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 4082</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>21098</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3038; 14204</t>
+          <t>2829; 15780</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7548; 19809</t>
+          <t>8918; 22656</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12944; 29710</t>
+          <t>14018; 30234</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6983</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1059; 10368</t>
+          <t>878; 8770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1267; 9444</t>
+          <t>1256; 9351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2997; 14343</t>
+          <t>3119; 13597</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8512</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1516; 16023</t>
+          <t>1452; 15905</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>868; 7840</t>
+          <t>896; 7690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3153; 18053</t>
+          <t>3428; 18470</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>0; 3615</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>0; 1959</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>361; 4031</t>
+          <t>378; 4052</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>0; 6579</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3319</t>
+          <t>0; 3543</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163; 5693</t>
+          <t>687; 6714</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11186</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2154; 13363</t>
+          <t>2244; 12812</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1286; 8775</t>
+          <t>2039; 9635</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4640; 18075</t>
+          <t>6011; 18379</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>38858</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7338; 31002</t>
+          <t>13723; 32289</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10161; 23979</t>
+          <t>11512; 27518</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18803; 47812</t>
+          <t>27686; 53334</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30468; 59263</t>
+          <t>34229; 63593</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28652; 53784</t>
+          <t>33638; 58000</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64779; 100895</t>
+          <t>75265; 114533</t>
         </is>
       </c>
     </row>
